--- a/docs/audits/tupelo-2026-08/MCTV_FieldSheet_Tupelo.xlsx
+++ b/docs/audits/tupelo-2026-08/MCTV_FieldSheet_Tupelo.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Sheet'!$A$1:$AC$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Sheet'!$A$1:$AA$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -496,24 +496,22 @@
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="40" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -574,92 +572,82 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t>Spoke with</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Card left?</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>Screen on?</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Content playing?</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Power test OK?</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Connection</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Presentation OK?</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Photos taken?</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>License # confirmed</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Label applied?</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Display brand</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Display model</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Size (in)</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>Mount type</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>Pi model</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>Pi serial</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>Power source</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>Label applied?</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
       <c r="Y1" s="2" t="inlineStr">
         <is>
-          <t>Issues found</t>
+          <t>Issues / notes</t>
         </is>
       </c>
       <c r="Z1" s="2" t="inlineStr">
         <is>
-          <t>Photo taken?</t>
+          <t>Audited by</t>
         </is>
       </c>
       <c r="AA1" s="2" t="inlineStr">
         <is>
-          <t>Audited by</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
           <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -723,8 +711,6 @@
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -786,8 +772,6 @@
       <c r="Y3" s="4" t="inlineStr"/>
       <c r="Z3" s="4" t="inlineStr"/>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -853,8 +837,6 @@
       <c r="Y4" s="4" t="inlineStr"/>
       <c r="Z4" s="4" t="inlineStr"/>
       <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -920,8 +902,6 @@
       <c r="Y5" s="4" t="inlineStr"/>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -983,8 +963,6 @@
       <c r="Y6" s="4" t="inlineStr"/>
       <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1050,8 +1028,6 @@
       <c r="Y7" s="4" t="inlineStr"/>
       <c r="Z7" s="4" t="inlineStr"/>
       <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1117,8 +1093,6 @@
       <c r="Y8" s="4" t="inlineStr"/>
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1176,8 +1150,6 @@
       <c r="Y9" s="4" t="inlineStr"/>
       <c r="Z9" s="4" t="inlineStr"/>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1243,8 +1215,6 @@
       <c r="Y10" s="4" t="inlineStr"/>
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1310,8 +1280,6 @@
       <c r="Y11" s="4" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1369,8 +1337,6 @@
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1428,8 +1394,6 @@
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1487,8 +1451,6 @@
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1554,8 +1516,6 @@
       <c r="Y15" s="4" t="inlineStr"/>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1617,8 +1577,6 @@
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1684,8 +1642,6 @@
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1751,8 +1707,6 @@
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1818,8 +1772,6 @@
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1881,8 +1833,6 @@
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1944,8 +1894,6 @@
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -2011,8 +1959,6 @@
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2078,8 +2024,6 @@
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -2141,8 +2085,6 @@
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -2208,8 +2150,6 @@
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -2271,8 +2211,6 @@
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -2326,8 +2264,6 @@
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -2381,8 +2317,6 @@
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -2430,8 +2364,6 @@
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2479,8 +2411,6 @@
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2528,8 +2458,6 @@
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -2577,8 +2505,6 @@
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -2626,8 +2552,6 @@
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -2675,41 +2599,33 @@
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC34"/>
-  <dataValidations count="10">
-    <dataValidation sqref="L2:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Screen on?" prompt="Is the display powered and showing something? 'No screen found' if the venue has no MCTV screen at all." type="list">
+  <autoFilter ref="A1:AA34"/>
+  <dataValidations count="8">
+    <dataValidation sqref="M2:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Card left?" prompt="Confirm you left an Exceed card so the venue knows who to call about the screen." type="list">
+      <formula1>"Yes,No - nobody available,No - card not accepted"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Screen on?" prompt="Is the display powered and showing something? 'No screen found' if the venue has no MCTV screen at all." type="list">
       <formula1>"Yes,No,No screen found"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content playing?" prompt="Is the MCTV loop actually advancing? Watch for at least two spot changes before answering." type="list">
+    <dataValidation sqref="O2:O34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content playing?" prompt="Is the MCTV loop actually advancing? Watch for at least two spot changes before answering." type="list">
       <formula1>"Yes,Frozen,Black,Error / no signal"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Orientation" prompt="How the display is hung. Our creative is built landscape; portrait screens letterbox." type="list">
-      <formula1>"Landscape,Portrait"</formula1>
+    <dataValidation sqref="P2:P34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Power test OK?" prompt="Power the unit down and back up, and confirm it returns to playing content on its own. This is the single most useful test in the audit." type="list">
+      <formula1>"Yes,No - did not come back,Not attempted"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Mount type" prompt="How it is fixed in place. Tells us what it costs to service or replace." type="list">
-      <formula1>"Wall,Ceiling,Stand,Shelf / counter,Other"</formula1>
+    <dataValidation sqref="Q2:Q34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Connection" prompt="How the Pi reaches the internet. 'Not connected' is a finding, not a failure — record it and move on." type="list">
+      <formula1>"Wi-Fi,Ethernet,Not connected"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Pi model" prompt="Raspberry Pi generation, printed on the board. 'Other / unmarked' is a fine answer." type="list">
-      <formula1>"Pi 3,Pi 4,Pi 5,Other / unmarked"</formula1>
+    <dataValidation sqref="R2:R34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Presentation OK?" prompt="Does the installation look sharp? Screen clean and clear of debris, cables concealed, nothing hanging loose." type="list">
+      <formula1>"Yes,Wires visible,Debris / dust,Wires + debris"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Power source" prompt="What the Pi is plugged into. TV USB ports cut power with the TV and cause 'dark screen' tickets." type="list">
-      <formula1>"Wall outlet,Power strip,TV USB port,PoE,Other"</formula1>
+    <dataValidation sqref="S2:S34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Photos taken?" prompt="Two shots: one wide enough to show the screen in its setting, one close on the Pi with its label." type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Network" prompt="How the Pi connects. Note the SSID in Notes if it is on venue guest Wi-Fi." type="list">
-      <formula1>"Wi-Fi,Ethernet,Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="W2:W34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Label applied?" prompt="Confirm the MCTV license label was affixed to this unit." type="list">
+    <dataValidation sqref="U2:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Label applied?" prompt="Confirm the MCTV label was affixed to this unit. That label doubles as the property and contact sticker." type="list">
       <formula1>"Yes,No - Pi not reachable,No - no label for this screen"</formula1>
-    </dataValidation>
-    <dataValidation sqref="X2:X34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Condition" prompt="Overall physical state of display and Pi together." type="list">
-      <formula1>"Good,Fair,Poor,Needs replacement"</formula1>
-    </dataValidation>
-    <dataValidation sqref="Z2:Z34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Photo taken?" prompt="One wide shot of the screen in place, one close shot of the Pi with its new label." type="list">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4557,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4574,7 +4490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-04</t>
+          <t>Generated 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4593,216 +4509,192 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Screen on?</t>
+          <t>Spoke with</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Is the display powered and showing something? 'No screen found' if the venue has no MCTV screen at all.</t>
+          <t>Name of the manager or staff member you introduced yourself to. This becomes our contact of record for the venue.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Content playing?</t>
+          <t>Card left?</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Is the MCTV loop actually advancing? Watch for at least two spot changes before answering.</t>
+          <t>Confirm you left an Exceed card so the venue knows who to call about the screen.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Display brand</t>
+          <t>Screen on?</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer on the bezel or the back label (Samsung, LG, TCL, Vizio...).</t>
+          <t>Is the display powered and showing something? 'No screen found' if the venue has no MCTV screen at all.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Display model</t>
+          <t>Content playing?</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Model number from the back label. Photograph it if it is hard to read.</t>
+          <t>Is the MCTV loop actually advancing? Watch for at least two spot changes before answering.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Size (in)</t>
+          <t>Power test OK?</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Diagonal screen size in inches. The model number usually starts with it.</t>
+          <t>Power the unit down and back up, and confirm it returns to playing content on its own. This is the single most useful test in the audit.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Orientation</t>
+          <t>Connection</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>How the display is hung. Our creative is built landscape; portrait screens letterbox.</t>
+          <t>How the Pi reaches the internet. 'Not connected' is a finding, not a failure — record it and move on.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Mount type</t>
+          <t>Presentation OK?</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>How it is fixed in place. Tells us what it costs to service or replace.</t>
+          <t>Does the installation look sharp? Screen clean and clear of debris, cables concealed, nothing hanging loose.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Pi model</t>
+          <t>Photos taken?</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Raspberry Pi generation, printed on the board. 'Other / unmarked' is a fine answer.</t>
+          <t>Two shots: one wide enough to show the screen in its setting, one close on the Pi with its label.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Pi serial</t>
+          <t>License # confirmed</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Serial from the Pi's own label, not the license number. Blank if the unit cannot be reached.</t>
+          <t>Write the license number from the Pi. It is pre-filled where we have it — confirm it matches, and correct it here if it does not.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Power source</t>
+          <t>Label applied?</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>What the Pi is plugged into. TV USB ports cut power with the TV and cause 'dark screen' tickets.</t>
+          <t>Confirm the MCTV label was affixed to this unit. That label doubles as the property and contact sticker.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Display brand</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>How the Pi connects. Note the SSID in Notes if it is on venue guest Wi-Fi.</t>
+          <t>Manufacturer on the bezel or the back label (Samsung, LG, TCL, Vizio...).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Label applied?</t>
+          <t>Display model</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Confirm the MCTV license label was affixed to this unit.</t>
+          <t>Model number from the back label. Photograph it if it is hard to read.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Size (in)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Overall physical state of display and Pi together.</t>
+          <t>Diagonal screen size in inches. The model number usually starts with it.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Issues found</t>
+          <t>Issues / notes</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Anything wrong: dark screen, wrong content, damaged mount, cables exposed, blocked sightline.</t>
+          <t>Anything wrong or worth knowing: dark screen, wrong content, exposed cables, blocked sightline, awkward access.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Photo taken?</t>
+          <t>Audited by</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>One wide shot of the screen in place, one close shot of the Pi with its new label.</t>
+          <t>Technician name.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Audited by</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Technician name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
           <t>Date of the visit (YYYY-MM-DD).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Anything the columns above do not cover — including who you spoke to.</t>
         </is>
       </c>
     </row>

--- a/docs/audits/tupelo-2026-08/MCTV_FieldSheet_Tupelo.xlsx
+++ b/docs/audits/tupelo-2026-08/MCTV_FieldSheet_Tupelo.xlsx
@@ -4490,7 +4490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07</t>
+          <t>Generated 2026-08-12</t>
         </is>
       </c>
     </row>
